--- a/artfynd/A 40499-2024 artfynd.xlsx
+++ b/artfynd/A 40499-2024 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119933435</v>
+        <v>119933443</v>
       </c>
       <c r="B3" t="n">
-        <v>5189</v>
+        <v>105009</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,32 +806,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580365</v>
+        <v>580326</v>
       </c>
       <c r="R3" t="n">
-        <v>6509034</v>
+        <v>6509081</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -874,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119933443</v>
+        <v>119933435</v>
       </c>
       <c r="B4" t="n">
-        <v>105009</v>
+        <v>5189</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,31 +926,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580326</v>
+        <v>580365</v>
       </c>
       <c r="R4" t="n">
-        <v>6509081</v>
+        <v>6509034</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 40499-2024 artfynd.xlsx
+++ b/artfynd/A 40499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119933437</v>
+        <v>119933438</v>
       </c>
       <c r="B2" t="n">
-        <v>91832</v>
+        <v>91836</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>4363</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stenkullen, Srm</t>
+          <t>Stenkullen, Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -724,7 +728,7 @@
         <v>6509126</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119933443</v>
+        <v>119933437</v>
       </c>
       <c r="B3" t="n">
-        <v>105009</v>
+        <v>91832</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,46 +806,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Srm</t>
+          <t>Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580326</v>
+        <v>580288</v>
       </c>
       <c r="R3" t="n">
-        <v>6509081</v>
+        <v>6509126</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -873,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1031,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119933438</v>
+        <v>119933443</v>
       </c>
       <c r="B5" t="n">
-        <v>91836</v>
+        <v>105009</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,30 +1046,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4363</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1078,13 +1078,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580288</v>
+        <v>580326</v>
       </c>
       <c r="R5" t="n">
-        <v>6509126</v>
+        <v>6509081</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 40499-2024 artfynd.xlsx
+++ b/artfynd/A 40499-2024 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119933435</v>
+        <v>119933443</v>
       </c>
       <c r="B4" t="n">
-        <v>5189</v>
+        <v>105009</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,32 +925,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -958,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580365</v>
+        <v>580326</v>
       </c>
       <c r="R4" t="n">
-        <v>6509034</v>
+        <v>6509081</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -993,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119933443</v>
+        <v>119933435</v>
       </c>
       <c r="B5" t="n">
-        <v>105009</v>
+        <v>5189</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,31 +1045,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580326</v>
+        <v>580365</v>
       </c>
       <c r="R5" t="n">
-        <v>6509081</v>
+        <v>6509034</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 40499-2024 artfynd.xlsx
+++ b/artfynd/A 40499-2024 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119933437</v>
+        <v>119933435</v>
       </c>
       <c r="B3" t="n">
-        <v>91832</v>
+        <v>5189</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,41 +806,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenkullen, Srm</t>
+          <t>Stenkullen, Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580288</v>
+        <v>580365</v>
       </c>
       <c r="R3" t="n">
-        <v>6509126</v>
+        <v>6509034</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -872,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1029,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119933435</v>
+        <v>119933437</v>
       </c>
       <c r="B5" t="n">
-        <v>5189</v>
+        <v>91832</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,47 +1047,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Srm</t>
+          <t>Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580365</v>
+        <v>580288</v>
       </c>
       <c r="R5" t="n">
-        <v>6509034</v>
+        <v>6509126</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 40499-2024 artfynd.xlsx
+++ b/artfynd/A 40499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119933438</v>
+        <v>119933435</v>
       </c>
       <c r="B2" t="n">
-        <v>91836</v>
+        <v>5189</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4363</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580288</v>
+        <v>580365</v>
       </c>
       <c r="R2" t="n">
-        <v>6509126</v>
+        <v>6509034</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119933435</v>
+        <v>119933437</v>
       </c>
       <c r="B3" t="n">
-        <v>5189</v>
+        <v>91850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,47 +808,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Srm</t>
+          <t>Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580365</v>
+        <v>580288</v>
       </c>
       <c r="R3" t="n">
-        <v>6509034</v>
+        <v>6509126</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -878,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119933443</v>
+        <v>119933438</v>
       </c>
       <c r="B4" t="n">
-        <v>105009</v>
+        <v>91854</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,31 +927,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>4363</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -963,13 +958,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580326</v>
+        <v>580288</v>
       </c>
       <c r="R4" t="n">
-        <v>6509081</v>
+        <v>6509126</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119933437</v>
+        <v>119933443</v>
       </c>
       <c r="B5" t="n">
-        <v>91832</v>
+        <v>105032</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,41 +1042,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenkullen, Srm</t>
+          <t>Stenkullen, Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580288</v>
+        <v>580326</v>
       </c>
       <c r="R5" t="n">
-        <v>6509126</v>
+        <v>6509081</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 40499-2024 artfynd.xlsx
+++ b/artfynd/A 40499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119933435</v>
+        <v>119933438</v>
       </c>
       <c r="B2" t="n">
-        <v>5189</v>
+        <v>91854</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,32 +691,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>4363</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580365</v>
+        <v>580288</v>
       </c>
       <c r="R2" t="n">
-        <v>6509034</v>
+        <v>6509126</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119933437</v>
+        <v>119933443</v>
       </c>
       <c r="B3" t="n">
-        <v>91850</v>
+        <v>105032</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,41 +806,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenkullen, Srm</t>
+          <t>Stenkullen, Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580288</v>
+        <v>580326</v>
       </c>
       <c r="R3" t="n">
-        <v>6509126</v>
+        <v>6509081</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -874,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119933438</v>
+        <v>119933437</v>
       </c>
       <c r="B4" t="n">
-        <v>91854</v>
+        <v>91850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,38 +926,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4363</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Srm</t>
+          <t>Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -964,7 +963,7 @@
         <v>6509126</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119933443</v>
+        <v>119933435</v>
       </c>
       <c r="B5" t="n">
-        <v>105032</v>
+        <v>5189</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,31 +1045,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580326</v>
+        <v>580365</v>
       </c>
       <c r="R5" t="n">
-        <v>6509081</v>
+        <v>6509034</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 40499-2024 artfynd.xlsx
+++ b/artfynd/A 40499-2024 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119933443</v>
+        <v>119933437</v>
       </c>
       <c r="B3" t="n">
-        <v>105032</v>
+        <v>91850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,46 +806,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Srm</t>
+          <t>Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580326</v>
+        <v>580288</v>
       </c>
       <c r="R3" t="n">
-        <v>6509081</v>
+        <v>6509126</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -877,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119933437</v>
+        <v>119933443</v>
       </c>
       <c r="B4" t="n">
-        <v>91850</v>
+        <v>105032</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,41 +921,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stenkullen, Srm</t>
+          <t>Stenkullen, Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580288</v>
+        <v>580326</v>
       </c>
       <c r="R4" t="n">
-        <v>6509126</v>
+        <v>6509081</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 40499-2024 artfynd.xlsx
+++ b/artfynd/A 40499-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1148,6 +1148,210 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120478010</v>
+      </c>
+      <c r="B6" t="n">
+        <v>94597</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stenkullen, Stenkullen, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>580321</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6509088</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120477950</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96198</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stenkullen, Stenkullen, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>580291</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6509129</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40499-2024 artfynd.xlsx
+++ b/artfynd/A 40499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119933438</v>
+        <v>119933435</v>
       </c>
       <c r="B2" t="n">
-        <v>91854</v>
+        <v>5189</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4363</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580288</v>
+        <v>580365</v>
       </c>
       <c r="R2" t="n">
-        <v>6509126</v>
+        <v>6509034</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119933437</v>
+        <v>119933443</v>
       </c>
       <c r="B3" t="n">
-        <v>91850</v>
+        <v>105032</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,41 +808,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenkullen, Srm</t>
+          <t>Stenkullen, Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580288</v>
+        <v>580326</v>
       </c>
       <c r="R3" t="n">
-        <v>6509126</v>
+        <v>6509081</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -872,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119933443</v>
+        <v>119933438</v>
       </c>
       <c r="B4" t="n">
-        <v>105032</v>
+        <v>91854</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,31 +932,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>4363</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,13 +963,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580326</v>
+        <v>580288</v>
       </c>
       <c r="R4" t="n">
-        <v>6509081</v>
+        <v>6509126</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119933435</v>
+        <v>119933437</v>
       </c>
       <c r="B5" t="n">
-        <v>5189</v>
+        <v>91850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,47 +1047,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Srm</t>
+          <t>Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580365</v>
+        <v>580288</v>
       </c>
       <c r="R5" t="n">
-        <v>6509034</v>
+        <v>6509126</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120478010</v>
+        <v>120477950</v>
       </c>
       <c r="B6" t="n">
-        <v>94597</v>
+        <v>96198</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,21 +1166,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580321</v>
+        <v>580291</v>
       </c>
       <c r="R6" t="n">
-        <v>6509088</v>
+        <v>6509129</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120477950</v>
+        <v>120478010</v>
       </c>
       <c r="B7" t="n">
-        <v>96198</v>
+        <v>94597</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>2170</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580291</v>
+        <v>580321</v>
       </c>
       <c r="R7" t="n">
-        <v>6509129</v>
+        <v>6509088</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 40499-2024 artfynd.xlsx
+++ b/artfynd/A 40499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119933435</v>
+        <v>119933443</v>
       </c>
       <c r="B2" t="n">
-        <v>5189</v>
+        <v>105032</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,32 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580365</v>
+        <v>580326</v>
       </c>
       <c r="R2" t="n">
-        <v>6509034</v>
+        <v>6509081</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119933443</v>
+        <v>119933437</v>
       </c>
       <c r="B3" t="n">
-        <v>105032</v>
+        <v>91850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,46 +807,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Srm</t>
+          <t>Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580326</v>
+        <v>580288</v>
       </c>
       <c r="R3" t="n">
-        <v>6509081</v>
+        <v>6509126</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -879,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1035,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119933437</v>
+        <v>119933435</v>
       </c>
       <c r="B5" t="n">
-        <v>91850</v>
+        <v>5189</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,41 +1041,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenkullen, Srm</t>
+          <t>Stenkullen, Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580288</v>
+        <v>580365</v>
       </c>
       <c r="R5" t="n">
-        <v>6509126</v>
+        <v>6509034</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120477950</v>
+        <v>120478010</v>
       </c>
       <c r="B6" t="n">
-        <v>96198</v>
+        <v>94597</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,21 +1166,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580291</v>
+        <v>580321</v>
       </c>
       <c r="R6" t="n">
-        <v>6509129</v>
+        <v>6509088</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120478010</v>
+        <v>120477950</v>
       </c>
       <c r="B7" t="n">
-        <v>94597</v>
+        <v>96198</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580321</v>
+        <v>580291</v>
       </c>
       <c r="R7" t="n">
-        <v>6509088</v>
+        <v>6509129</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 40499-2024 artfynd.xlsx
+++ b/artfynd/A 40499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119933443</v>
+        <v>119933435</v>
       </c>
       <c r="B2" t="n">
-        <v>105032</v>
+        <v>5189</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580326</v>
+        <v>580365</v>
       </c>
       <c r="R2" t="n">
-        <v>6509081</v>
+        <v>6509034</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -758,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119933437</v>
+        <v>119933443</v>
       </c>
       <c r="B3" t="n">
-        <v>91850</v>
+        <v>105032</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,41 +808,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenkullen, Srm</t>
+          <t>Stenkullen, Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580288</v>
+        <v>580326</v>
       </c>
       <c r="R3" t="n">
-        <v>6509126</v>
+        <v>6509081</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -873,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119933438</v>
+        <v>119933437</v>
       </c>
       <c r="B4" t="n">
-        <v>91854</v>
+        <v>91850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,38 +928,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4363</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Srm</t>
+          <t>Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -963,7 +965,7 @@
         <v>6509126</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119933435</v>
+        <v>119933438</v>
       </c>
       <c r="B5" t="n">
-        <v>5189</v>
+        <v>91854</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,32 +1047,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>4363</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1078,13 +1078,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580365</v>
+        <v>580288</v>
       </c>
       <c r="R5" t="n">
-        <v>6509034</v>
+        <v>6509126</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120478010</v>
+        <v>120477950</v>
       </c>
       <c r="B6" t="n">
-        <v>94597</v>
+        <v>96198</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,21 +1166,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580321</v>
+        <v>580291</v>
       </c>
       <c r="R6" t="n">
-        <v>6509088</v>
+        <v>6509129</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120477950</v>
+        <v>120478010</v>
       </c>
       <c r="B7" t="n">
-        <v>96198</v>
+        <v>94597</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>2170</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580291</v>
+        <v>580321</v>
       </c>
       <c r="R7" t="n">
-        <v>6509129</v>
+        <v>6509088</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
